--- a/output/roomself_excel/11246.xlsx
+++ b/output/roomself_excel/11246.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>125580</v>
+        <v>107663</v>
       </c>
       <c r="D2" t="n">
-        <v>2924</v>
+        <v>2820</v>
       </c>
       <c r="E2" t="n">
-        <v>501</v>
+        <v>398</v>
       </c>
       <c r="F2" t="n">
-        <v>299</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>122190</v>
+        <v>267915</v>
       </c>
       <c r="D3" t="n">
-        <v>3044</v>
+        <v>4416</v>
       </c>
       <c r="E3" t="n">
         <v>700</v>
       </c>
       <c r="F3" t="n">
-        <v>276</v>
+        <v>471</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>325208</v>
+        <v>122190</v>
       </c>
       <c r="D4" t="n">
-        <v>6040</v>
+        <v>3044</v>
       </c>
       <c r="E4" t="n">
-        <v>713</v>
+        <v>700</v>
       </c>
       <c r="F4" t="n">
-        <v>700</v>
+        <v>276</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>107663</v>
+        <v>86875</v>
       </c>
       <c r="D5" t="n">
-        <v>2820</v>
+        <v>2480</v>
       </c>
       <c r="E5" t="n">
-        <v>398</v>
+        <v>360</v>
       </c>
       <c r="F5" t="n">
-        <v>23</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6">
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>86875</v>
+        <v>113914</v>
       </c>
       <c r="D6" t="n">
-        <v>2480</v>
+        <v>3020</v>
       </c>
       <c r="E6" t="n">
-        <v>360</v>
+        <v>412</v>
       </c>
       <c r="F6" t="n">
-        <v>306</v>
+        <v>340</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>32166</v>
+        <v>10877</v>
       </c>
       <c r="D7" t="n">
-        <v>1732</v>
+        <v>888</v>
       </c>
       <c r="E7" t="n">
-        <v>214</v>
+        <v>149</v>
       </c>
       <c r="F7" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>113914</v>
+        <v>100914</v>
       </c>
       <c r="D8" t="n">
-        <v>3020</v>
+        <v>2564</v>
       </c>
       <c r="E8" t="n">
-        <v>700</v>
+        <v>363</v>
       </c>
       <c r="F8" t="n">
-        <v>412</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>35200</v>
+        <v>125580</v>
       </c>
       <c r="D9" t="n">
-        <v>1504</v>
+        <v>2924</v>
       </c>
       <c r="E9" t="n">
-        <v>200</v>
+        <v>501</v>
       </c>
       <c r="F9" t="n">
-        <v>22</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10877</v>
+        <v>32166</v>
       </c>
       <c r="D10" t="n">
-        <v>888</v>
+        <v>1732</v>
       </c>
       <c r="E10" t="n">
-        <v>149</v>
+        <v>214</v>
       </c>
       <c r="F10" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -668,16 +668,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4453</v>
+        <v>57293</v>
       </c>
       <c r="D11" t="n">
-        <v>536</v>
+        <v>2224</v>
       </c>
       <c r="E11" t="n">
-        <v>61</v>
+        <v>209</v>
       </c>
       <c r="F11" t="n">
-        <v>22</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12">
@@ -690,16 +690,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>134151</v>
+        <v>35200</v>
       </c>
       <c r="D12" t="n">
-        <v>3008</v>
+        <v>1504</v>
       </c>
       <c r="E12" t="n">
-        <v>507</v>
+        <v>200</v>
       </c>
       <c r="F12" t="n">
-        <v>314</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -712,16 +712,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>45130</v>
+        <v>4453</v>
       </c>
       <c r="D13" t="n">
-        <v>1764</v>
+        <v>536</v>
       </c>
       <c r="E13" t="n">
-        <v>264</v>
+        <v>61</v>
       </c>
       <c r="F13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>100914</v>
+        <v>134151</v>
       </c>
       <c r="D14" t="n">
-        <v>2564</v>
+        <v>3008</v>
       </c>
       <c r="E14" t="n">
-        <v>363</v>
+        <v>507</v>
       </c>
       <c r="F14" t="n">
-        <v>23</v>
+        <v>314</v>
       </c>
     </row>
     <row r="15">
@@ -756,13 +756,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>45066</v>
+        <v>45130</v>
       </c>
       <c r="D15" t="n">
-        <v>1900</v>
+        <v>1764</v>
       </c>
       <c r="E15" t="n">
-        <v>162</v>
+        <v>264</v>
       </c>
       <c r="F15" t="n">
         <v>23</v>
@@ -778,16 +778,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>78269</v>
+        <v>45066</v>
       </c>
       <c r="D16" t="n">
-        <v>2400</v>
+        <v>1900</v>
       </c>
       <c r="E16" t="n">
-        <v>310</v>
+        <v>162</v>
       </c>
       <c r="F16" t="n">
-        <v>257</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -800,16 +800,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>71544</v>
+        <v>78269</v>
       </c>
       <c r="D17" t="n">
-        <v>2140</v>
+        <v>2400</v>
       </c>
       <c r="E17" t="n">
-        <v>254</v>
+        <v>310</v>
       </c>
       <c r="F17" t="n">
-        <v>23</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18">
@@ -822,16 +822,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>59196</v>
+        <v>71544</v>
       </c>
       <c r="D18" t="n">
-        <v>2476</v>
+        <v>2140</v>
       </c>
       <c r="E18" t="n">
-        <v>507</v>
+        <v>254</v>
       </c>
       <c r="F18" t="n">
-        <v>333</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19">
@@ -844,16 +844,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>78287</v>
+        <v>59196</v>
       </c>
       <c r="D19" t="n">
-        <v>2616</v>
+        <v>2476</v>
       </c>
       <c r="E19" t="n">
-        <v>347</v>
+        <v>250</v>
       </c>
       <c r="F19" t="n">
-        <v>21</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20">
@@ -866,16 +866,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>54416</v>
+        <v>78287</v>
       </c>
       <c r="D20" t="n">
-        <v>1932</v>
+        <v>2616</v>
       </c>
       <c r="E20" t="n">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -888,15 +888,37 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>76254</v>
+        <v>54416</v>
       </c>
       <c r="D21" t="n">
-        <v>2420</v>
+        <v>1932</v>
       </c>
       <c r="E21" t="n">
         <v>179</v>
       </c>
       <c r="F21" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>76254</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2420</v>
+      </c>
+      <c r="E22" t="n">
+        <v>179</v>
+      </c>
+      <c r="F22" t="n">
         <v>23</v>
       </c>
     </row>

--- a/output/roomself_excel/11246.xlsx
+++ b/output/roomself_excel/11246.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,23 @@
       <c r="D2" t="n">
         <v>2820</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>398</v>
       </c>
-      <c r="F2" t="n">
-        <v>23</v>
-      </c>
+      <c r="G2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,11 +543,38 @@
       <c r="D3" t="n">
         <v>4416</v>
       </c>
-      <c r="E3" t="n">
-        <v>700</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>471</v>
+        <v>449</v>
+      </c>
+      <c r="G3" t="n">
+        <v>23</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>177</v>
+      </c>
+      <c r="J3" t="n">
+        <v>22</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>309</v>
+      </c>
+      <c r="M3" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -519,12 +592,23 @@
       <c r="D4" t="n">
         <v>3044</v>
       </c>
-      <c r="E4" t="n">
-        <v>700</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>276</v>
-      </c>
+        <v>541</v>
+      </c>
+      <c r="G4" t="n">
+        <v>23</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +625,31 @@
       <c r="D5" t="n">
         <v>2480</v>
       </c>
-      <c r="E5" t="n">
-        <v>360</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>306</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="G5" t="n">
+        <v>23</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>337</v>
+      </c>
+      <c r="J5" t="n">
+        <v>23</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +666,31 @@
       <c r="D6" t="n">
         <v>3020</v>
       </c>
-      <c r="E6" t="n">
-        <v>412</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>340</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="G6" t="n">
+        <v>23</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>389</v>
+      </c>
+      <c r="J6" t="n">
+        <v>22</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +707,23 @@
       <c r="D7" t="n">
         <v>888</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>149</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>22</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +740,23 @@
       <c r="D8" t="n">
         <v>2564</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>363</v>
       </c>
-      <c r="F8" t="n">
-        <v>23</v>
-      </c>
+      <c r="G8" t="n">
+        <v>23</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +773,31 @@
       <c r="D9" t="n">
         <v>2924</v>
       </c>
-      <c r="E9" t="n">
-        <v>501</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>299</v>
-      </c>
+        <v>552</v>
+      </c>
+      <c r="G9" t="n">
+        <v>23</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>455</v>
+      </c>
+      <c r="J9" t="n">
+        <v>23</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +814,15 @@
       <c r="D10" t="n">
         <v>1732</v>
       </c>
-      <c r="E10" t="n">
-        <v>214</v>
-      </c>
-      <c r="F10" t="n">
-        <v>11</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +839,15 @@
       <c r="D11" t="n">
         <v>2224</v>
       </c>
-      <c r="E11" t="n">
-        <v>209</v>
-      </c>
-      <c r="F11" t="n">
-        <v>171</v>
-      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +864,23 @@
       <c r="D12" t="n">
         <v>1504</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>200</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>22</v>
       </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +897,23 @@
       <c r="D13" t="n">
         <v>536</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>61</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>22</v>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +930,31 @@
       <c r="D14" t="n">
         <v>3008</v>
       </c>
-      <c r="E14" t="n">
-        <v>507</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>314</v>
-      </c>
+        <v>582</v>
+      </c>
+      <c r="G14" t="n">
+        <v>23</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>461</v>
+      </c>
+      <c r="J14" t="n">
+        <v>23</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +971,23 @@
       <c r="D15" t="n">
         <v>1764</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>264</v>
       </c>
-      <c r="F15" t="n">
-        <v>23</v>
-      </c>
+      <c r="G15" t="n">
+        <v>23</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +1004,23 @@
       <c r="D16" t="n">
         <v>1900</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
         <v>162</v>
       </c>
-      <c r="F16" t="n">
-        <v>23</v>
-      </c>
+      <c r="G16" t="n">
+        <v>23</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +1037,31 @@
       <c r="D17" t="n">
         <v>2400</v>
       </c>
-      <c r="E17" t="n">
-        <v>310</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>257</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="G17" t="n">
+        <v>23</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>219</v>
+      </c>
+      <c r="J17" t="n">
+        <v>23</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +1078,23 @@
       <c r="D18" t="n">
         <v>2140</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
         <v>254</v>
       </c>
-      <c r="F18" t="n">
-        <v>23</v>
-      </c>
+      <c r="G18" t="n">
+        <v>23</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +1111,31 @@
       <c r="D19" t="n">
         <v>2476</v>
       </c>
-      <c r="E19" t="n">
-        <v>250</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F19" t="n">
-        <v>103</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="G19" t="n">
+        <v>23</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>80</v>
+      </c>
+      <c r="J19" t="n">
+        <v>23</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +1152,15 @@
       <c r="D20" t="n">
         <v>2616</v>
       </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,12 +1177,31 @@
       <c r="D21" t="n">
         <v>1932</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
         <v>179</v>
       </c>
-      <c r="F21" t="n">
-        <v>23</v>
-      </c>
+      <c r="G21" t="n">
+        <v>23</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>304</v>
+      </c>
+      <c r="J21" t="n">
+        <v>19</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -915,12 +1218,31 @@
       <c r="D22" t="n">
         <v>2420</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
         <v>179</v>
       </c>
-      <c r="F22" t="n">
-        <v>23</v>
-      </c>
+      <c r="G22" t="n">
+        <v>23</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>426</v>
+      </c>
+      <c r="J22" t="n">
+        <v>19</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
